--- a/data/ams_weekly_data/White_Mulberry/ads_report_week28.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week28.xlsx
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4252.06</v>
+        <v>4250.18</v>
       </c>
       <c r="E3" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F3" t="n">
-        <v>47220</v>
+        <v>47217</v>
       </c>
       <c r="G3" t="n">
         <v>7202.54</v>
@@ -731,7 +731,7 @@
         <v>218</v>
       </c>
       <c r="F11" t="n">
-        <v>51800</v>
+        <v>51799</v>
       </c>
       <c r="G11" t="n">
         <v>26329.67</v>
@@ -815,7 +815,7 @@
         <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>12114</v>
+        <v>12110</v>
       </c>
       <c r="G14" t="n">
         <v>20129.66</v>
@@ -843,7 +843,7 @@
         <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>16701</v>
+        <v>16697</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>130</v>
       </c>
       <c r="F18" t="n">
-        <v>32153</v>
+        <v>32152</v>
       </c>
       <c r="G18" t="n">
         <v>55053.38</v>
@@ -1067,7 +1067,7 @@
         <v>213</v>
       </c>
       <c r="F23" t="n">
-        <v>21731</v>
+        <v>21730</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>187</v>
       </c>
       <c r="F24" t="n">
-        <v>18572</v>
+        <v>18571</v>
       </c>
       <c r="G24" t="n">
         <v>51180.5</v>
@@ -1126,10 +1126,10 @@
         <v>36137</v>
       </c>
       <c r="G25" t="n">
-        <v>14233.9</v>
+        <v>7202.54</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1291,7 +1291,7 @@
         <v>262</v>
       </c>
       <c r="F31" t="n">
-        <v>134722</v>
+        <v>134717</v>
       </c>
       <c r="G31" t="n">
         <v>14415.22</v>
@@ -1350,10 +1350,10 @@
         <v>16833</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1518,10 +1518,10 @@
         <v>27936</v>
       </c>
       <c r="G39" t="n">
-        <v>17701.71</v>
+        <v>20327.98</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1851,13 +1851,13 @@
         <v>213</v>
       </c>
       <c r="F51" t="n">
-        <v>73578</v>
+        <v>73570</v>
       </c>
       <c r="G51" t="n">
         <v>28176.27</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -1935,7 +1935,7 @@
         <v>121</v>
       </c>
       <c r="F54" t="n">
-        <v>8828</v>
+        <v>8827</v>
       </c>
       <c r="G54" t="n">
         <v>9318.639999999999</v>
@@ -2047,13 +2047,13 @@
         <v>52</v>
       </c>
       <c r="F58" t="n">
-        <v>8759</v>
+        <v>8754</v>
       </c>
       <c r="G58" t="n">
-        <v>9191.530000000001</v>
+        <v>6565.26</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2131,7 +2131,7 @@
         <v>14</v>
       </c>
       <c r="F61" t="n">
-        <v>3979</v>
+        <v>3977</v>
       </c>
       <c r="G61" t="n">
         <v>3143.22</v>
@@ -2299,7 +2299,7 @@
         <v>80</v>
       </c>
       <c r="F67" t="n">
-        <v>6644</v>
+        <v>6643</v>
       </c>
       <c r="G67" t="n">
         <v>1694.07</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4523.87</v>
+        <v>4503.36</v>
       </c>
       <c r="E68" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F68" t="n">
-        <v>12026</v>
+        <v>12025</v>
       </c>
       <c r="G68" t="n">
         <v>17829.65</v>
@@ -2554,10 +2554,10 @@
         <v>14633</v>
       </c>
       <c r="G76" t="n">
-        <v>8808.51</v>
+        <v>8180.54</v>
       </c>
       <c r="H76" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
@@ -2579,13 +2579,13 @@
         <v>232</v>
       </c>
       <c r="F77" t="n">
-        <v>100632</v>
+        <v>100631</v>
       </c>
       <c r="G77" t="n">
-        <v>9532.200000000001</v>
+        <v>10039.83</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2887,7 +2887,7 @@
         <v>90</v>
       </c>
       <c r="F88" t="n">
-        <v>15008</v>
+        <v>15007</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>222</v>
       </c>
       <c r="F89" t="n">
-        <v>59702</v>
+        <v>59701</v>
       </c>
       <c r="G89" t="n">
         <v>7077.97</v>
@@ -2943,7 +2943,7 @@
         <v>267</v>
       </c>
       <c r="F90" t="n">
-        <v>39652</v>
+        <v>39651</v>
       </c>
       <c r="G90" t="n">
         <v>24355.09</v>
@@ -2971,7 +2971,7 @@
         <v>87</v>
       </c>
       <c r="F91" t="n">
-        <v>13022</v>
+        <v>13021</v>
       </c>
       <c r="G91" t="n">
         <v>5379.66</v>
@@ -3394,10 +3394,10 @@
         <v>9837</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3531,13 +3531,13 @@
         <v>56</v>
       </c>
       <c r="F111" t="n">
-        <v>8411</v>
+        <v>8410</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>627.97</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -4063,7 +4063,7 @@
         <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>13494</v>
+        <v>13493</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,23 +4867,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>214</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>6.635000000000001</v>
+        <v>39.81</v>
       </c>
       <c r="G7" t="n">
-        <v>460.875</v>
+        <v>2765.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4895,28 +4895,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>12728</v>
       </c>
       <c r="E8" t="n">
+        <v>132</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2168.308142173432</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6819.49</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6.635000000000001</v>
-      </c>
-      <c r="G8" t="n">
-        <v>460.875</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4928,28 +4928,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4JG97R</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>8885</v>
       </c>
       <c r="E9" t="n">
+        <v>92</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1513.531857826568</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4760.17</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6.635000000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>460.875</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -4961,28 +4961,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>13418</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="F10" t="n">
-        <v>6.635000000000001</v>
+        <v>2020.183794726039</v>
       </c>
       <c r="G10" t="n">
-        <v>460.875</v>
+        <v>10898.28</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4994,28 +4994,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>3233</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>6.635000000000001</v>
+        <v>486.8262052739609</v>
       </c>
       <c r="G11" t="n">
-        <v>460.875</v>
+        <v>2626.28</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -5027,28 +5027,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>9345</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
-        <v>6.635000000000001</v>
+        <v>2364.94</v>
       </c>
       <c r="G12" t="n">
-        <v>460.875</v>
+        <v>6565.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5069,19 +5069,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21613</v>
+        <v>23890</v>
       </c>
       <c r="E13" t="n">
-        <v>224</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
-        <v>3681.84</v>
+        <v>1403.431089372207</v>
       </c>
       <c r="G13" t="n">
-        <v>11579.66</v>
+        <v>5912.270613669449</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -5093,228 +5093,30 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16651</v>
+        <v>14706</v>
       </c>
       <c r="E14" t="n">
-        <v>222</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>2507.01</v>
+        <v>863.8989106277926</v>
       </c>
       <c r="G14" t="n">
-        <v>13524.56</v>
+        <v>3639.369386330551</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>9345</v>
-      </c>
-      <c r="E15" t="n">
-        <v>149</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2364.94</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6565.25</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>7719</v>
-      </c>
-      <c r="E16" t="n">
-        <v>35</v>
-      </c>
-      <c r="F16" t="n">
-        <v>453.466</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1910.328</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>7719</v>
-      </c>
-      <c r="E17" t="n">
-        <v>35</v>
-      </c>
-      <c r="F17" t="n">
-        <v>453.466</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1910.328</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>7719</v>
-      </c>
-      <c r="E18" t="n">
-        <v>35</v>
-      </c>
-      <c r="F18" t="n">
-        <v>453.466</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1910.328</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>7719</v>
-      </c>
-      <c r="E19" t="n">
-        <v>35</v>
-      </c>
-      <c r="F19" t="n">
-        <v>453.466</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1910.328</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>7719</v>
-      </c>
-      <c r="E20" t="n">
-        <v>35</v>
-      </c>
-      <c r="F20" t="n">
-        <v>453.466</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1910.328</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
